--- a/Bd.xlsx
+++ b/Bd.xlsx
@@ -5,18 +5,22 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Descargas\German Mestizo\Catalogo de productos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Antigravity\WeWebApp\Dr_GermanMestizo_NutriHeal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB58E76C-97DF-4887-8A43-7B18E05600FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1F9FDB-3652-4965-A1B8-A93EEDF77954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AF5044E2-1B3D-4E12-8406-E59E91CACD17}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="NutriVita" sheetId="1" r:id="rId1"/>
+    <sheet name="Nutra" sheetId="3" r:id="rId2"/>
+    <sheet name="GreenLab" sheetId="2" r:id="rId3"/>
+    <sheet name="Boiron" sheetId="4" r:id="rId4"/>
+    <sheet name="Atopeel" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$F$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NutriVita!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="554">
   <si>
     <t>Suplementos dietarios</t>
   </si>
@@ -674,13 +678,1406 @@
   </si>
   <si>
     <t>Subcategoría o Grupo</t>
+  </si>
+  <si>
+    <t>Bebidas Funcionales</t>
+  </si>
+  <si>
+    <t>COLAGM MAX</t>
+  </si>
+  <si>
+    <t>Presentacion</t>
+  </si>
+  <si>
+    <t>VTFRKANCE</t>
+  </si>
+  <si>
+    <t>* Ideal para combatir infecciones urinarias.
+* Fortalece el sistema inmune.
+* Desintoxica el cuerpo contra organismos nocivos.
+* Reduce la incidencia de infecciones recurrentes del trato urinario.
+Bebida con arándano, mora y uva.</t>
+  </si>
+  <si>
+    <t>CRANBERRY</t>
+  </si>
+  <si>
+    <t>SD2011-000204</t>
+  </si>
+  <si>
+    <t>SD2019-0004482</t>
+  </si>
+  <si>
+    <t>SD2010-0001668</t>
+  </si>
+  <si>
+    <t>CRANNUTRA</t>
+  </si>
+  <si>
+    <t>SD2024-0004748</t>
+  </si>
+  <si>
+    <t>Suplementos Nutracéuticos</t>
+  </si>
+  <si>
+    <t>Salud Urinaria y Antioxidante</t>
+  </si>
+  <si>
+    <t>Beneficios: Refuerzo del sistema inmunológico. Protección antioxidante sistémica. Complemento en prevención y tratamiento de infecciones urinarias recurrentes. Apoyo funcional del tracto urinario.
+Composición: Vaccinum Vitis-Idaea (Arándano rojo europeo) 280 mg, Vitamina C 200 mg, Vitamina E natural (D-alfa tocoferol) 6 UI, Rose Hips 10 mg.</t>
+  </si>
+  <si>
+    <t>IMMUNOL</t>
+  </si>
+  <si>
+    <t>Beneficios: Fortalecimiento del sistema inmunológico. Soporte en estrés físico, infecciones recurrentes y fatiga. Apoyo a la salud intestinal y de mucosas. Regulación de la respuesta inflamatoria.
+Composición: Maitake (Grifola frondosa) 50 mg, Shiitake (Lentinula edodes) 15 mg, Cordyceps sinensis 15 mg, Reishi (Ganoderma lucidum) 50 mg, Calostro bovino 200 mg.</t>
+  </si>
+  <si>
+    <t>Salud Capilar, Cutánea y Ungueal</t>
+  </si>
+  <si>
+    <t>KPILLUS</t>
+  </si>
+  <si>
+    <t>SD2021-0004574</t>
+  </si>
+  <si>
+    <t>Beneficios: Salud capilar, cutánea y ungueal. Integridad celular. Soporte metabólico (metabolismo de glucosa, oxidación de ácidos grasos y producción de energía celular - ATP). Indicado en cambios hormonales, estrés crónico, postparto y dietas restrictivas.
+Composición: Biotina (cofactor esencial).</t>
+  </si>
+  <si>
+    <t>Energía y Digestión</t>
+  </si>
+  <si>
+    <t>VITA B</t>
+  </si>
+  <si>
+    <t>SD2011-0002163</t>
+  </si>
+  <si>
+    <t>Beneficios: Mejora del rendimiento metabólico. Mejora la absorción proteica. Soporte digestivo en dispepsia leve. Ayuda a reducir la pesadez posprandial. Apoyo en fatiga física y mental.
+Composición: Vitaminas del complejo B + Papaína.</t>
+  </si>
+  <si>
+    <t>Salud Neurológica</t>
+  </si>
+  <si>
+    <t>MECOBAL</t>
+  </si>
+  <si>
+    <t>Beneficios: Neuropatías periféricas y dolor neuropático. Apoyo en trastornos del estado de ánimo. Déficit funcional de vitamina B12. Fatiga crónica y bajo rendimiento cognitivo. Pacientes con alteraciones de metilación.
+Composición: Metilcobalamina (forma activa y biodisponible de vitamina B12; no requiere conversión hepática).</t>
+  </si>
+  <si>
+    <t>Suplementos Dietarios</t>
+  </si>
+  <si>
+    <t>Minerales – Salud Muscular y Nerviosa</t>
+  </si>
+  <si>
+    <t>NUTRAMAG</t>
+  </si>
+  <si>
+    <t>Beneficios: Apoyo a la función muscular y nerviosa, relajación y metabolismo energético.
+Composición: Magnesio 400 mg (formas aspartato, lactato y citrato). Suplemento dietario.</t>
+  </si>
+  <si>
+    <t>Metabolismo – Control Glucémico</t>
+  </si>
+  <si>
+    <t>CHROMONATE</t>
+  </si>
+  <si>
+    <t>Beneficios: Apoyo al metabolismo de los carbohidratos y al control de los niveles de glucosa.
+Composición: Cromo (picolinato de cromo). Suplemento dietario. (Dosis en mcg no legible en el material; verificar en etiqueta.)</t>
+  </si>
+  <si>
+    <t>Salud Ósea</t>
+  </si>
+  <si>
+    <t>SYNERVIT</t>
+  </si>
+  <si>
+    <t>Beneficios: Apoyo a la salud ósea y a la correcta fijación del calcio.
+Composición: Vitamina D3 + Vitamina K2. Suplemento dietario.</t>
+  </si>
+  <si>
+    <t>Salud Articular y de la Piel</t>
+  </si>
+  <si>
+    <t>NUTRAGEN</t>
+  </si>
+  <si>
+    <t>Beneficios: Apoyo a la salud articular, de la piel y de los tejidos conectivos.
+Composición: Colágeno hidrolizado + Vitamina C. Suplemento dietario.</t>
+  </si>
+  <si>
+    <t>VITAMIN C 1000 + ZINC</t>
+  </si>
+  <si>
+    <t>Beneficios: Soporte del sistema inmunológico y acción antioxidante.
+Composición: Vitamina C 1000 mg + Zinc. Suplemento dietario.</t>
+  </si>
+  <si>
+    <t>Minerales – Sistema Inmunológico</t>
+  </si>
+  <si>
+    <t>NUTRAZINC</t>
+  </si>
+  <si>
+    <t>Beneficios: Soporte del sistema inmunológico y de la salud celular.
+Composición: Zinc 40 mg. Suplemento dietario. (Verificar número de registro completo en etiqueta.)</t>
+  </si>
+  <si>
+    <t>Medicamentos Homeopáticos (Boiron)</t>
+  </si>
+  <si>
+    <t>Anímicos</t>
+  </si>
+  <si>
+    <t>SEDATIF PC</t>
+  </si>
+  <si>
+    <t>MH2018-0000704-R1</t>
+  </si>
+  <si>
+    <t>Indicación: Coadyuvante en el tratamiento de los estados nerviosos y trastorno del sueño.
+Posología: Disolver en la boca 2 comprimidos 3 veces al día
+Composición: Aconitum napellus 6 CH, Belladonna 6 CH, Caléndula officinalis 6 CH, Chelidonium majus 6 CH, Abrus precatorius 6 CH, Viburnum opulus 6 CH.
+Presentación: Comprimidos</t>
+  </si>
+  <si>
+    <t>Argentum nitricum 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Nerviosismo por anticipación, con precipitación y agitación. Diarrea emotiva.
+Posología: 5 gránulos 3 veces al día.
+Composición: Argentum nitricum 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Gelsemium sempervirens 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Nerviosismo por anticipación, con precipitación y agitación. Diarrea emotiva.
+Posología: 5 gránulos la víspera, una hora antes y en el momento del acontecimiento.
+Composición: Gelsemium sempervirens 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Ignatia amara 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Ansiedad con espasmos. Comportamiento paradójico. Hipersensibilidad. Insomnio.
+Posología: 5 gránulos la víspera, una hora antes y en el momento del acontecimiento.
+Composición: Ignatia amara 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Acidum phosphoricum 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Desánimo y agotamiento intelectual con apatía.
+Posología: 5 gránulos 2 o 3 veces al día.
+Composición: Acidum phosphoricum 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Coffea cruda 15 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Insomnio por hiperactividad mental, afluencia continua de pensamientos, excitación intelectual. Insomnio tras recibir una buena noticia.
+Posología: 5 gránulos una hora antes de acostarse.
+Composición: Coffea cruda 15 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Kalium bromatum 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Terrores nocturnos con agitación y ansiedad.
+Posología: 5 gránulos una hora antes de acostarse y 5 gránulos al acostarse.
+Composición: Kalium bromatum 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Nux vomica 15 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Dificultad para dormir, insomnio por sobreactividad y estrés. Desvelo hacia las tres de la mañana.
+Posología: 5 gránulos por la noche.
+Composición: Nux vomica 15 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>QUIETUDE</t>
+  </si>
+  <si>
+    <t>MH2009-0001098</t>
+  </si>
+  <si>
+    <t>Indicación: Trastornos menores del sueño. Ansiedad pasajera en el niño. Hiperemotividad y estrés.
+Posología: Vía oral. Una cucharadita (5 ml) en la mañana y en la noche durante 10 días. Interrumpir al desaparecer los síntomas.
+Composición: Chamomilla vulgaris 9 CH, Hyoscyamus niger 9 CH, Kalium bromatum 9 CH, Passiflora incarnata 3 CH, Stramonium 9 CH.
+Presentación: Jarabe x 200 ml</t>
+  </si>
+  <si>
+    <t>Stramonium 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Insomnio debido a terrores nocturnos con miedo a la oscuridad.
+Posología: 5 gránulos una hora antes de acostarse y 5 gránulos al acostarse.
+Composición: Stramonium 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Circulatorios</t>
+  </si>
+  <si>
+    <t>Aesculus hippocastanum 5 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Congestión venosa hemorroidal con sensación de pesadez. Hemorroides con prurito.
+Posología: 5 gránulos 4 veces al día.
+Composición: Aesculus hippocastanum 5 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Hamamelis virginiana 5 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Congestión venosa agravada por los movimientos. Varices.
+Posología: 5 gránulos 2 veces al día.
+Composición: Hamamelis virginiana 5 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Pulsatilla 5 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Piernas cansadas y dilatación venosa que empeora con el calor y la inmovilidad.
+Posología: 5 gránulos 2 veces al día.
+Composición: Pulsatilla 5 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Dermatológicos</t>
+  </si>
+  <si>
+    <t>Graphites 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Eczemas en pliegues y uniones cutáneo-mucosas, con secreciones de apariencia melosa que sangran. Cicatrices queloides.
+Posología: 5 gránulos 2 veces al día.
+Composición: Graphites 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Belladonna 5 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Quemaduras leves y de primer grado.
+Posología: 5 gránulos 3 veces al día.
+Composición: Belladonna 5 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Cantharis 5 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Quemaduras de segundo grado y ampollas ardientes en los pies (marcha, deporte).
+Posología: 5 gránulos 4 veces al día.
+Composición: Cantharis 5 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Apis mellifica 15 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Picaduras de insectos con edema y prurito, que se alivian con aplicaciones de agua fría.
+Posología: 5 gránulos 2 veces al día.
+Composición: Apis mellifica 15 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Ledum palustre 5 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Picaduras de insectos.
+Posología: 5 gránulos 4 veces al día.
+Composición: Ledum palustre 5 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Indicación: Eritema en las extremidades causado por el frío.
+Posología: 5 gránulos 3 veces al día.
+Composición: Pulsatilla 5 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Thuya occidentalis 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Tratamiento de fondo de las verrugas.
+Posología: 5 gránulos 1 vez al día.
+Composición: Thuya occidentalis 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Urtica urens 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Urticarias alérgicas o tóxicas con edema, que empeoran con el agua fría.
+Posología: 5 gránulos 3 veces al día.
+Composición: Urtica urens 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Digestivos</t>
+  </si>
+  <si>
+    <t>GASTROCYNESINE</t>
+  </si>
+  <si>
+    <t>MH2009-0000984</t>
+  </si>
+  <si>
+    <t>Indicación: Acidez gástrica. Somnolencia después de las comidas. Reflujo gastroesofágico.
+Posología: Disolver en la boca 2 comprimidos 15 minutos antes de las comidas. Repetir si es necesario después de las comidas.
+Composición: Abies nigra 4 CH, Carbo vegetabilis 4 CH, Nux vomica 4 CH, Robinia pseudoacacia 4 CH.
+Presentación: Comprimidos</t>
+  </si>
+  <si>
+    <t>Antimonium crudum 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Indigestión, diarrea por excesos alimentarios. Lengua con capa blanca.
+Posología: 5 gránulos 3 veces al día.
+Composición: Antimonium crudum 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Carbo vegetabilis 5 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Aerofagia, pesadez de estómago provocadas por el alcohol y los alimentos grasos.
+Posología: 5 gránulos 1 vez al día.
+Composición: Carbo vegetabilis 5 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Nux vomica 5 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Molestias digestivas por excesos alimentarios, de alcohol, café o tabaco. Pesadez gástrica.
+Posología: 5 gránulos 2 veces al día.
+Composición: Nux vomica 5 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>China rubra 5 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Diarrea sin dolor, con agotamiento, por consumo excesivo de fruta.
+Posología: 5 gránulos 3 veces al día.
+Composición: China rubra 5 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Indicación: Colon irritable, espasmos intestinales.
+Posología: 5 gránulos 2 veces al día.
+Composición: Ignatia amara 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Podophyllum peltatum 5 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en casos de diarrea profusa, fétida, matutina, de origen hepático.
+Posología: 5 gránulos 3 veces al día.
+Composición: Podophyllum peltatum 5 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Cina 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en caso de cólicos abdominales debidos a vermes (Lombrices) con Nerviosismo, Insomnio.
+Posología: 5 gránulos 2 veces al día.
+Composición: Cina 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Ginecológicos</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en caso de nauseas del embarazo por el olor de la comida o del tabaco y que se calman comiendo.
+Posología: 5 gránulos 2 veces al día.
+Composición: Ignatia amara 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Sepia oficinalis 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en caso de nauseas matinales del embarazo, pensando o viendo alimentos.
+Posología: 5 gránulos 1 vez al día.
+Composición: Sepia oficinalis 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Apis mellifica 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en casos de inflamación de los pechos durante la subida de leche. Se alterna con Bryonia 9 CH.
+Posología: 5 gránulos 2 veces al día.
+Composición: Apis mellifica 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Bryonia alba 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en casos de inflamación dolorosa de las mamas durante la subida de leche, que empeora con el menor movimiento. Se alterna con Apis 9 CH.
+Posología: 5 gránulos 2 veces al día.
+Composición: Bryonia alba 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en la preparación al parto. Rigidez cervical, dolor uterino. Anomalía de las contracciones con ansiedad.
+Posología: 5 gránulos 2 veces al día.
+Composición: Gelsemium sempervirens 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Caulophyllum 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en la preparación al parto. Rigidez del cérvix (favorece la dilatación). Se aconseja alternarlo con Actaea.
+Posología: 5 gránulos cada 2 horas.
+Composición: Caulophyllum 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Lachesis mutus 5 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en caso de sofocos y modificaciones del humor en la perimenopausia. Cefalea congestiva y pulsátil.
+Posología: 5 gránulos 3 veces al día.
+Composición: Lachesis mutus 5 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Actaea racemosa 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en caso de dismenorrea progresiva a lo largo de la regla, calambroidea con síndrome premenstrual.
+Posología: 5 gránulos 3 veces al día.
+Composición: Actaea racemosa 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Caulophyllum 5 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en caso de dismenorrea del primer día, rigidez del cérvix.
+Posología: 5 gránulos 3 veces al día.
+Composición: Caulophyllum 5 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Colocynthis 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en caso de dismenorrea espasmódica calambroidea que mejora con la presión y el calor, después de una contrariedad o de una emoción.
+Posología: 5 gránulos 4 veces al día.
+Composición: Colocynthis 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Folliculinum 15 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en caso de síndrome premenstrual.
+Posología: 1 dosis los días 8 y 18 del ciclo.
+Composición: Folliculinum 15 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Osteomusculares</t>
+  </si>
+  <si>
+    <t>Cuprum metallicum 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en caso de calambres nocturnos (de las pantorrillas), de comienzo y final bruscos.
+Posología: 5 gránulos 2 veces al día.
+Composición: Cuprum metallicum 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Kalium phosphoricum 5 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en caso de cansancio físico e intelectual, agotamiento e insomnio.
+Posología: 5 gránulos 3 veces al día.
+Composición: Kalium phosphoricum 5 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Indicación: Descalcificación, problemas del crecimiento. Consolidación de las fracturas. Convalecencia.
+Posología: 2 comprimidos 2 o 3 veces al día.
+Composición: Calcarea ostreica 3 DH, Calcarea fluorica 3 DH, Calcarea phosphorica 3 DH, Sulfuriodatum 4 CH.
+Presentación: Comprimidos</t>
+  </si>
+  <si>
+    <t>Calcarea phosphorica 5 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en casos de consolidación de las fracturas.
+Posología: 5 gránulos 3 veces al día.
+Composición: Calcarea phosphorica 5 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Silicea 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en casos de desmineralización y descalcificación con gran sensibilidad al frío.
+Posología: 5 gránulos una vez al día.
+Composición: Silicea 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en casos de hinchazón de una articulación por acumulación de líquido acuoso, de instalación rápida con edema rojizo que mejora con el frío.
+Posología: En casos agudos, 5 gránulos cada 15 minutos, espaciando según mejoría; en casos subagudos 2 a 4 tomas al día.
+Composición: Apis mellifica 15 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en casos de dolores articulares que empeoran con el movimiento y mejoran con el reposo y las aplicaciones frías.
+Posología: 5 gránulos cada hora, espaciando según mejoría.
+Composición: Bryonia alba 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Rhus toxicodendron 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en casos de dolores articulares, periarticulares, tendinosos y ligamentosos provocados por humedad y sobreesfuerzos, que mejoran con el movimiento progresivo y empeoran con el inicio del movimiento y el reposo.
+Posología: 5 gránulos 3 veces al día.
+Composición: Rhus toxicodendron 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Ruta graveolens 5 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en casos de esguinces y luxaciones.
+Posología: 5 gránulos 3 veces al día.
+Composición: Ruta graveolens 5 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Arnica montana 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en casos de contusiones y traumatismos de todo tipo y tejido. Cansancio muscular. Daños capilares y venosos.
+Posología: 5 gránulos 3 veces al día.
+Composición: Arnica montana 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en casos de equimosis por traumatismo (ojo negro…).
+Posología: 5 gránulos 4 veces al día.
+Composición: Ledum palustre 5 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Symphytum 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado para la consolidación de fracturas y episodios dolorosos del hueso y periostio.
+Posología: 5 gránulos 4 veces al día.
+Composición: Symphytum 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Respiratorios</t>
+  </si>
+  <si>
+    <t>Belladonna 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en casos de anginas agudas, con inflamación de color rojo intenso, de aparición brusca y con abatimiento.
+Posología: 5 gránulos 4 veces al día.
+Composición: Belladonna 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>OSCILLOCOCCINUM</t>
+  </si>
+  <si>
+    <t>MH2019-0000697-R1</t>
+  </si>
+  <si>
+    <t>Indicación: Tratamiento preventivo y curativo de la gripe y de los estados gripales: escalofríos, fiebre, dolor de cabeza.
+Posología: Preventivo: una dosis a la semana de octubre a febrero. Inicio: una dosis en cuanto aparezcan los primeros síntomas, repetir cada 6 horas 2 o 3 veces. Estados declarados: una dosis por la mañana y otra por la noche durante 3 días.
+Composición: Anas barbariae hepatis et cordis extractum 200 K.
+Presentación: Dosis de glóbulos</t>
+  </si>
+  <si>
+    <t>Aconitum napellus 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en casos de fiebre alta de aparición brusca sin transpiración.
+Posología: 5 gránulos 2 a 4 veces al día.
+Composición: Aconitum napellus 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en casos de fiebre alta de aparición brusca, a veces oscilante, con sudores profusos, cefalea pulsátil.
+Posología: 5 gránulos 2 a 4 veces al día.
+Composición: Belladonna 9 CH
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en casos de fiebre en meseta, sin sed, con escalofríos, temblores, dolores musculares y postración.
+Posología: 5 gránulos 2 a 4 veces al día.
+Composición: Gelsemium sempervirens 9 CH
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Indicación: Catarros con predominio de estornudos y rinorrea. Rinitis. Rinitis alérgicas.
+Posología: Disolver en la boca 1 comprimido cada hora; espaciar las tomas según mejoría.
+Composición: Allium cepa 5 CH, Belladonna 5 CH, Sabadilla 5 CH, Kalium bichromicum 5 CH, Gelsemium sempervirens 5 CH.
+Presentación: Comprimidos</t>
+  </si>
+  <si>
+    <t>Allium cepa 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en caso de catarro con rinorrea irritante y lagrimeo no irritante.
+Posología: 5 gránulos cada 2 horas, espaciando según mejoría.
+Composición: Allium cepa 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Kalium bichromicum 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en caso de rinitis que cursa con dolor y presión en la raíz nasal. Moco espeso, viscoso, amarillo o amarillo verdoso; a veces sanguinolento, pegajoso, que puede formar costras en las fosas nasales.
+Posología: 5 gránulos 3 veces al día.
+Composición: Kalium bichromicum 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Kalium sulfuricum 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en caso de rinitis. Inflamación de las vías respiratorias superiores con rinorrea amarillenta o amarillo verdosa que empeora con el calor.
+Posología: 5 gránulos 3 veces al día.
+Composición: Kalium sulfuricum 9 CH
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en caso de sinusitis maxilar y frontal que empeora con el frío, con moco espeso, viscoso y amarillo verdoso.
+Posología: 5 gránulos 3 veces al día.
+Composición: Kalium bichromicum 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>STODALINE (Jarabe)</t>
+  </si>
+  <si>
+    <t>MH2020-0002728</t>
+  </si>
+  <si>
+    <t>Indicación: Tratamiento sintomático de la tos seca y productiva.
+Posología: Adultos: 15 ml de 3 a 5 veces al día. Niños: 5 ml de 3 a 5 veces al día. Espaciar según mejoría.
+Composición: Antimonium tartaricum 6 CH, Bryonia 3 CH, Coccus cacti 4 CH, Drosera 3 CH, Ipeca 3 CH, Rumex crispus 6 CH, Spongia tosta 4 CH, Sticta pulmonaria 3 CH.
+Presentación: Jarabe x 200 ml.</t>
+  </si>
+  <si>
+    <t>Antimonium tartaricum 5 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en caso de inflamación de las vías respiratorias superiores con expectoración difícil.
+Posología: 5 gránulos cada 2 horas, espaciando según mejoría.
+Composición: Antimonium tartaricum 5 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Drosera 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en caso de tos quintosa espasmódica, por la noche y con el calor.
+Posología: 5 gránulos después de cada quinta de tos.
+Composición: Drosera 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Rumex crispus 5 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en caso de tos seca al respirar aire frío.
+Posología: 5 gránulos cada 2 horas.
+Composición: Rumex crispus 5 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Sambucus nigra 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en caso de tos asmática, tos espasmódica y disnea asmática nocturna.
+Posología: 5 gránulos cada 10 minutos hasta mejoría.
+Composición: Sambucus nigra 9 CH
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Spongia tosta 5 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en caso de tos asmática, tos espasmódica e inflamación de las cuerdas vocales.
+Posología: 5 gránulos después de cada quinta de tos.
+Composición: Spongia tosta 5 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Urinarios</t>
+  </si>
+  <si>
+    <t>Cantharis vesicatoria 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Utilizado en caso de infección urinaria aguda con dolor antes y durante la micción.
+Posología: 5 gránulos 4 veces al día.
+Composición: Cantharis vesicatoria 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Otras Patologías</t>
+  </si>
+  <si>
+    <t>Borax 5 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Utilizado en caso de aftas en la parte interna de la mejilla con líquido opaco.
+Posología: 5 gránulos 3 veces al día.
+Composición: Borax 5 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Cocculus indicus 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en caso de mareo en vehículos que mejora con el calor o cerrando las ventanillas.
+Posología: 5 gránulos una hora antes de la salida y repetir al inicio del viaje; repetir según necesidad.
+Composición: Cocculus indicus 9 CH
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Euphrasia oficinalis 5 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en caso de conjuntivitis con lagrimeo irritante y coriza no irritante. Inflamación de los párpados.
+Posología: 5 gránulos cada 2 horas, espaciando según mejoría.
+Composición: Euphrasia oficinalis 5 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Chamomilla vulgaris 15 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en caso de dolor, irritabilidad y diarrea debidas a la dentición.
+Posología: 5 gránulos cada 15 minutos, espaciando según mejoría. Disolver en el biberón o en un poco de agua.
+Composición: Chamomilla vulgaris 15 CH
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>China rubra 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado como adyuvante en caso de hemorragias y anemia hiposiderémica.
+Posología: 5 gránulos 3 veces al día.
+Composición: China rubra 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Phosphorus 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado como adyuvante en caso de hemorragias abundantes y repetidas en las diferentes mucosas y en heridas.
+Posología: 5 gránulos cada 6 horas.
+Composición: Phosphorus 9 CH
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en caso de insolación. Cefaleas congestivas pulsátiles. Enrojecimiento de la cara con sudores.
+Posología: 5 gránulos 3 veces al día.
+Composición: Belladonna 9 CH.
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Argentum nitricum 30 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en caso de miedo por anticipación con agitación y precipitación, con diarrea emotiva. Insomnio.
+Posología: Una dosis la víspera por la tarde y otra dosis una hora antes de la intervención.
+Composición: Argentum nitricum 30 CH
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Gelsemium sempervirens 30 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en caso de miedo por anticipación a una intervención.
+Posología: Una dosis la víspera por la tarde y otra dosis una hora antes de la intervención.
+Composición: Gelsemium sempervirens 30 CH
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en cuidados postoperatorios para reducir el dolor y la inflamación.
+Posología: 5 gránulos cada hora, espaciando según mejoría.
+Composición: Arnica montana 9 CH
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado en caso de adinamia de las convalecencias.
+Posología: 5 gránulos 2 veces al día.
+Composición: China rubra 9 CH
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>Staphysagria 9 CH</t>
+  </si>
+  <si>
+    <t>Indicación: Frecuentemente utilizado para aliviar los dolores postoperatorios (heridas quirúrgicas, incisiones, entre otros).
+Posología: 5 gránulos 2 veces al día.
+Composición: Staphysagria 9 CH
+Presentación: Gránulos: tubo de 4g</t>
+  </si>
+  <si>
+    <t>OST</t>
+  </si>
+  <si>
+    <t>COR</t>
+  </si>
+  <si>
+    <t>Piel, Huesos y Articulaciones</t>
+  </si>
+  <si>
+    <t>600ml</t>
+  </si>
+  <si>
+    <t>* Hidrata y mejora la elasticidad y la firmeza de la piel.
+* Retrasa el envejecimiento y previene las arrugas.
+* Contribuye a la salud de huesos y las articulaciones.
+* Fortalece las uñas y el cabello.
+Bebida a base de agua con romero, uva, colágeno hidrolizado y resveratrol.</t>
+  </si>
+  <si>
+    <t>Migraña y Energía</t>
+  </si>
+  <si>
+    <t>* Ideal para la migraña y los fuertes dolores de cabeza.
+* Ayuda al sistema inmunológico.
+* Actúa eficazmente sobre el cansancio y agotamiento visual.
+* Reconstituyente del cerebro y de los glóbulos rojos.
+Bebida a base de agua con canela y fresa.</t>
+  </si>
+  <si>
+    <t>Salud Urinaria e Inmune</t>
+  </si>
+  <si>
+    <t>Digestivo y Detox</t>
+  </si>
+  <si>
+    <t>GOLZAN</t>
+  </si>
+  <si>
+    <t>* Desinfla el intestino y elimina el exceso de gases.
+* Mejora el metabolismo gástrico.
+* Ayuda a mejorar el tránsito intestinal.
+* Ayuda a eliminar toxinas del colon e intestinos.
+Bebida con concentrado de ciruela, concentrado de pitaya, concentrado de piña, fibra de manzana e inulina</t>
+  </si>
+  <si>
+    <t>Huesos y Sistema Nervioso</t>
+  </si>
+  <si>
+    <t>CITRATO DE MAGNESIO</t>
+  </si>
+  <si>
+    <t>* Promueve la regeneración celular y previene la osteoporosis.
+* Ayuda a fijar el calcio en los huesos además de combatir y prevenir infecciones.
+* Actúa eficazmente sobre el cansancio y agotamiento visual.
+* Promueve el bienestar de los huesos, los músculos, el sistema nervioso y previene lesiones musculares.
+Bebida a base de agua con alfalfa, mandarina, colágeno hidrolizado y cúrcuma.</t>
+  </si>
+  <si>
+    <t>Respiratorio (Tos y Flemas)</t>
+  </si>
+  <si>
+    <t>TOMIMIEL</t>
+  </si>
+  <si>
+    <t>* Ayuda a expulsar la tos seca.
+* Ayuda a expulsar flemas.
+* Ayuda a descongestionar el pecho.
+Miel de abeja 100 % natural que ayuda a aliviar síntomas. Bebida con naranja, menta, limoncillo, cebolla y miel de abejas.</t>
+  </si>
+  <si>
+    <t>Nutrición Infantil (Hierro)</t>
+  </si>
+  <si>
+    <t>FERRIZTOM</t>
+  </si>
+  <si>
+    <t>* Ayuda a fortalecer las defensas del organismo.
+* Ayuda a obtener energía.
+* Proporciona los nutrientes necesarios para el desarrollo físico y mental de los niños en su etapa de crecimiento.
+Bebida con concentrado de guayaba y maní fortificada con hierro.</t>
+  </si>
+  <si>
+    <t>Energía y Apoyo Nutricional</t>
+  </si>
+  <si>
+    <t>SOMIESUR</t>
+  </si>
+  <si>
+    <t>* Mejora tu estado físico.
+* Ayuda al sistema inmunológico.
+* Apoyo nutricional para tu cuerpo.
+Bebida con concentrado de fresa.</t>
+  </si>
+  <si>
+    <t>Control de Peso y Glucosa</t>
+  </si>
+  <si>
+    <t>YACÓN</t>
+  </si>
+  <si>
+    <t>* Favorece a las personas con resistencia a la insulina.
+* Apoya dietas de adelgazamiento.
+* Mejora el sistema inmune.
+* Protege las células del daño oxidativo.
+Bebida a base de agua con fenogreco, ciruela, yacón y berenjena.</t>
+  </si>
+  <si>
+    <t>Hígado y Digestión</t>
+  </si>
+  <si>
+    <t>ALCACHOFA</t>
+  </si>
+  <si>
+    <t>* Ayuda a digerir grasas y producción de bilis.
+* Protege el hígado favoreciendo las células hepáticas.
+* Favorece la eliminación de líquidos en el cuerpo.
+* Rica en antioxidantes.
+Bebida a base de agua con clavo de olor, apio, alcachofa y cardamomo.</t>
+  </si>
+  <si>
+    <t>Ácido Úrico y Piel (Detox)</t>
+  </si>
+  <si>
+    <t>CHOLAGGE</t>
+  </si>
+  <si>
+    <t>* Favorece la eliminación del exceso de ácido úrico.
+* Alivia los dolores reumáticos y la gota.
+* Ayuda a combatir impurezas de la piel (acné, eczemas, forúnculos, urticarias y dermatosis).
+Bebida a base de agua con espirulina, limón y espinaca.</t>
+  </si>
+  <si>
+    <t>Antioxidante (Piel y Corazón)</t>
+  </si>
+  <si>
+    <t>RESVERATROL</t>
+  </si>
+  <si>
+    <t>350ml</t>
+  </si>
+  <si>
+    <t>* Potente antioxidante que evita el envejecimiento celular.
+* Ayuda a proteger el corazón y la salud arterial.
+* Ayuda en la producción de colágeno.
+* Mejora el tono y brillo de la piel.
+Bebida con concentrado de uva y colágeno hidrolizado fortificado con vitamina E.</t>
+  </si>
+  <si>
+    <t>Quema de Grasa y Detox</t>
+  </si>
+  <si>
+    <t>DELGW</t>
+  </si>
+  <si>
+    <t>* Excelente quemador de grasa.
+* Antiinflamatorio.
+* Regulador de los niveles de colesterol y triglicéridos.
+* Mejora la digestión.
+* Es auxiliar en el tratamiento del intestino perezoso.
+* Desinflamante del hígado.
+* Desintoxica la sangre.
+* Limpia las venas de la glucosa.
+Bebida a base de agua con pimienta negra, limón, cúrcuma y jengibre.</t>
+  </si>
+  <si>
+    <t>Antiparasitario y Digestivo</t>
+  </si>
+  <si>
+    <t>PETIPON</t>
+  </si>
+  <si>
+    <t>100ml</t>
+  </si>
+  <si>
+    <t>* Apoya la eliminación de parásitos intestinales.
+* Ayuda a la limpieza del sistema digestivo.
+* Favorece una digestión más ligera.
+* Contribuye a reducir malestar abdominal.
+* Elaborado con ingredientes naturales.
+Bebida con concentrado de pitaya, papaya y piña con ajo.</t>
+  </si>
+  <si>
+    <t>Salud Sexual Masculina</t>
+  </si>
+  <si>
+    <t>KING K - GOLDD</t>
+  </si>
+  <si>
+    <t>* Aumenta el deseo y la sensación de placer sexual.
+* Para deportistas de alto rendimiento.
+* Erecciones más fuertes y prolongadas.
+* Despierta la líbido y deseo sexual.
+* Elimina la frigidez y la astenia sexual.
+Bebida con borojó, chontaduro y maca.</t>
+  </si>
+  <si>
+    <t>SIX-TOR</t>
+  </si>
+  <si>
+    <t>* Alarga y engrosa el pene en el momento de la relación.
+* Retrasa la eyaculación.
+* Mejora las erecciones, promoviendo el óxido nítrico.
+* Aumenta la irrigación de sangre al pene, excelente vasodilatador.
+Bebida con concentrado de borojó, concentrado de chontaduro y maca, fortificado con vitamina B1.</t>
+  </si>
+  <si>
+    <t>FERME VIT F</t>
+  </si>
+  <si>
+    <t>500ml</t>
+  </si>
+  <si>
+    <t>* Favorece el aumento del tamaño y grosor del pene durante el encuentro sexual.
+* Ayuda a prolongar el tiempo antes de la eyaculación, mejorando el control.
+* Potencia la firmeza de las erecciones al estimular la producción de óxido nítrico.
+* Incrementa el flujo sanguíneo hacia el pene gracias a su potente efecto vasodilatador.
+Alimento líquido a base de agua endulzado con estevia, con pulpa de borojó y chontaduro deshidratados.</t>
+  </si>
+  <si>
+    <t>Articular y Antiinflamatorio</t>
+  </si>
+  <si>
+    <t>GREENCOLG</t>
+  </si>
+  <si>
+    <t>* Fortalece los huesos, las articulaciones y las uñas. Excelente antiinflamatorio.
+* Interviene en la reparación del tejido cartilaginoso.
+* Alivia los dolores producidos por la artritis, artrosis y dolores articulares.
+Bebida con fresa, colágeno hidrolizado y cúrcuma.</t>
+  </si>
+  <si>
+    <t>Articular y Óseo</t>
+  </si>
+  <si>
+    <t>GAF - PLUS</t>
+  </si>
+  <si>
+    <t>300ml</t>
+  </si>
+  <si>
+    <t>* Ayuda en dolores como: Fibromialgia, Hombros, Brazos, Cuello, Espalda, Manos y Pies, Rodillas, Artritis y Artrosis.
+Bebida con fresa, colágeno hidrolizado y cúrcuma.</t>
+  </si>
+  <si>
+    <t>Alimento en Polvo</t>
+  </si>
+  <si>
+    <t>Nutrición Infantil e Inmune</t>
+  </si>
+  <si>
+    <t>BIFANTIL</t>
+  </si>
+  <si>
+    <t>800g</t>
+  </si>
+  <si>
+    <t>* Refuerza el sistema inmunológico.
+* Previene enfermedades respiratorias.
+* Incrementa el crecimiento.
+* Regula el apetito.
+Alimento en polvo a base de avena con guayaba fortificado con vitamina C.</t>
+  </si>
+  <si>
+    <t>Energía y Proteína</t>
+  </si>
+  <si>
+    <t>DEFENSE</t>
+  </si>
+  <si>
+    <t>* Energía 100%.
+Alimento en polvo a base de avena con proteína concentrada de suero y colágeno hidrolizado fortificado con calcio.</t>
+  </si>
+  <si>
+    <t>Función Cerebral (B1)</t>
+  </si>
+  <si>
+    <t>VIT FRANS</t>
+  </si>
+  <si>
+    <t>* Fortalece las funciones del cerebro, actuando como un reconstituyente cerebral evitando la pérdida de memoria.
+Alimento en polvo a base de avena fortificado con B1.</t>
+  </si>
+  <si>
+    <t>Huesos e Inmune</t>
+  </si>
+  <si>
+    <t>COLÁGENO MARINO</t>
+  </si>
+  <si>
+    <t>* Buena condición física que debe complementarse con entrenamiento.
+* Mejor condición cognitiva.
+* Fortalecimiento del sistema óseo.
+* Refuerzo del sistema inmunológico.
+Alimento en polvo a base de avena con uva fortificado con vitamina D.</t>
+  </si>
+  <si>
+    <t>Piel, Cabello y Articulaciones</t>
+  </si>
+  <si>
+    <t>COL100PRO</t>
+  </si>
+  <si>
+    <t>* Actúa en la piel como antienvejecimiento.
+* Ayuda a fortalecer cabellos y uñas.
+* Tratamiento de colágeno para las articulaciones.
+* Fortifica los huesos.
+Alimento en polvo a base de avena con colágeno hidrolizado fortificado con vitamina E.</t>
+  </si>
+  <si>
+    <t>Fibra (Colesterol y Glucosa)</t>
+  </si>
+  <si>
+    <t>FIBRA MAX</t>
+  </si>
+  <si>
+    <t>800g y 450g</t>
+  </si>
+  <si>
+    <t>* Reduce los niveles de colesterol y glucosa en la sangre.
+Linaza con psyllium, alcachofa en polvo, noni polvo, té verde, semillas de chía.</t>
+  </si>
+  <si>
+    <t>Huesos (Calcio y Vit. D)</t>
+  </si>
+  <si>
+    <t>MULTICAL D</t>
+  </si>
+  <si>
+    <t>* Previene la osteoporosis.
+* Protege dientes y huesos.
+Alimento en polvo a base de avena con sacha inchi fortificado con vitamina D.</t>
+  </si>
+  <si>
+    <t>Inmune y Energía</t>
+  </si>
+  <si>
+    <t>CALOSTRO BOVINO PLUS</t>
+  </si>
+  <si>
+    <t>* Ayuda al sistema inmune.
+* Aumenta energía.
+Alimento en polvo a base de avena con calostro bovino y colágeno hidrolizado fortificado con magnesio.</t>
+  </si>
+  <si>
+    <t>Inmune y Antioxidante</t>
+  </si>
+  <si>
+    <t>GANODERMA</t>
+  </si>
+  <si>
+    <t>* Es anticancerígeno y combate tumores, quistes y miomas.
+* Purifica y oxigena la sangre y neutraliza los radicales libres.
+* Fortalece el sistema inmune del cuerpo.
+Alimento en polvo a base de avena fortificado con vitamina B1, B2 y B6.</t>
+  </si>
+  <si>
+    <t>* Potente antioxidante que evita el envejecimiento celular.
+* Ayuda a proteger el corazón y la salud arterial.
+* Ayuda en la producción de colágeno.
+* Mejora el tono y brillo de la piel.
+Alimento en polvo a base de avena con colágeno hidrolizado fortificado con vitamina E.</t>
+  </si>
+  <si>
+    <t>Homeopáticos</t>
+  </si>
+  <si>
+    <t>Estrés y Energía</t>
+  </si>
+  <si>
+    <t>Ashwagandha</t>
+  </si>
+  <si>
+    <t>* Equilibrio para tu ritmo de vida.
+* Ayuda a manejar el estrés diario, apoya la energía natural y fortalece el bienestar integral.
+* Vive con calma y enfoque.</t>
+  </si>
+  <si>
+    <t>Defensas / Inmune</t>
+  </si>
+  <si>
+    <t>Echinacea</t>
+  </si>
+  <si>
+    <t>* Defensas que florecen contigo.
+* Apoya el equilibrio natural del cuerpo y ayuda a fortalecer el sistema inmune día a día.
+* Tu aliado natural en cada temporada.</t>
+  </si>
+  <si>
+    <t>Concentración y Enfoque</t>
+  </si>
+  <si>
+    <t>Melena de León</t>
+  </si>
+  <si>
+    <t>* Claridad que se siente desde adentro.
+* Ayuda a fortalecer la concentración, apoya el enfoque mental y acompaña tu bienestar diario.
+* Conecta con tu mejor versión.</t>
+  </si>
+  <si>
+    <t>Bienestar y Alivio (Tópico)</t>
+  </si>
+  <si>
+    <t>Cannabis Sativa (Uso Tópico)</t>
+  </si>
+  <si>
+    <t>* Bienestar que se siente en la piel.
+* Ayuda a relajar el cuerpo, apoya la sensación de alivio y fortalece el equilibrio natural.
+* Naturaleza que acompaña tu día.
+Cannabis Sativa · Uso Tópico.</t>
+  </si>
+  <si>
+    <t>RESVERATROL (Sachet)</t>
+  </si>
+  <si>
+    <t>30mL</t>
+  </si>
+  <si>
+    <t>Presentación</t>
+  </si>
+  <si>
+    <t>Dermocosméticos (Atopeel)</t>
+  </si>
+  <si>
+    <t>Cuidado Facial / Barrera Cutánea</t>
+  </si>
+  <si>
+    <t>Atopeel Crema</t>
+  </si>
+  <si>
+    <t>Hidratación Corporal</t>
+  </si>
+  <si>
+    <t>Atopeel Body</t>
+  </si>
+  <si>
+    <t>200 ml</t>
+  </si>
+  <si>
+    <t>Limpieza Facial</t>
+  </si>
+  <si>
+    <t>Atopeel Agua Micelar 5 en 1</t>
+  </si>
+  <si>
+    <t>Crema de Noche / Antiedad</t>
+  </si>
+  <si>
+    <t>Atopeel-N Crema Noche</t>
+  </si>
+  <si>
+    <t>Protección Solar</t>
+  </si>
+  <si>
+    <t>Atopeel S Ultraprotect Sun</t>
+  </si>
+  <si>
+    <t>220 mL</t>
+  </si>
+  <si>
+    <t>Beneficios: Limpieza profunda y suave para mantener la barrera cutánea. Acción 5 en 1: desmaquilla, hidrata, matifica, limpia y tonifica el rostro. Elimina la polución. 0% alcohol y 0% jabón. Apta para rostro, labios y ojos. Dermatológica y oftalmológicamente testeada. 98% ingredientes de origen natural (100% origen vegano).
+Ingredientes activos: NatraGem S (micelas que limpian sin irritar el rostro, labios y ojos) y Trehalose 100 (ingrediente de última generación que mejora la función de la barrera cutánea promoviendo la formación de estructuras lamelares, humecta disminuyendo la pérdida transepidérmica de agua —TEWL— en el estrato córneo y reduce los niveles de Interleuquina 1).</t>
+  </si>
+  <si>
+    <t>50 g</t>
+  </si>
+  <si>
+    <t>Beneficios: Crema facial antiedad de fórmula multicomponente con 6 ingredientes de origen natural que proporcionan reparación epidérmica y regulan la melanogénesis. Antienvejecimiento, efecto reparador, humectante, antioxidante, antiglicante y despigmentante. Reduce un 40% la producción de melanina, estimula el metabolismo celular del colágeno y aumenta la resistencia de la membrana celular frente a los radicales libres. Dermatológicamente probado, no comedogénico. 92% ingredientes de origen natural.
+Ingredientes activos: Ácido hialurónico de origen vegetal (hidrata en 3 niveles), Vitamina C 10%, Retinol 0,5% (reduce líneas finas; mejora biodisponibilidad, estabilidad y eficiencia del colágeno), Niacinamida 2% (disminuye la permeabilidad vascular; aumenta la producción de colágeno I, III y V; despigmentante), Ascorbosilane C (antioxidante y reductor de manchas), Silicio (potencia penetración, estabilidad y biodisponibilidad de la vitamina C), Vitamina E 1% (antioxidante) y Ormagel SH (hidratante; aumenta la tolerabilidad de los demás componentes).</t>
+  </si>
+  <si>
+    <t>Sérum Antiedad / Antioxidante</t>
+  </si>
+  <si>
+    <t>Atopeel C Professional Serum</t>
+  </si>
+  <si>
+    <t>30 g</t>
+  </si>
+  <si>
+    <t>Beneficios: Sérum facial antioxidante de triple acción —hidratante, antioxidante y antiedad— para un resplandor natural. Fórmula innovadora a base de algas marinas que hidratan y proporcionan firmeza incluso en pieles sensibles. Reduce un 40% la producción de melanina, estimula el metabolismo celular del colágeno, reduce la pérdida transepidérmica de agua, mejora la elasticidad y disminuye las arrugas. Para todo tipo de piel. 90% ingredientes de origen natural.
+Ingredientes activos: Vitamina C 10% + Ácido hialurónico 10%. Ascorbosilane C (vitamina C al 10% combinada con Silicio para mejorar penetración, estabilidad y biodisponibilidad), Ácido hialurónico vegano de 3 pesos moleculares (hidrata dermis y epidermis en múltiples niveles) y algas marinas rojas y marrones (aumentan la humectación, suavidad y elasticidad).</t>
+  </si>
+  <si>
+    <t>50 g — SPF 50+ (3 tonos)</t>
+  </si>
+  <si>
+    <t>Beneficios: Protector solar de amplio espectro SPF 50+ (UVA, UVB, IR y luz visible). Activa la protección de la piel, restaura el daño previamente ocasionado e hidrata: protege, previene, repara e hidrata. Fotoprotección de espectro total con Repair Complex. Reduce un 74% el daño cutáneo por luz visible y radiación infrarroja. Textura ligera de rápida absorción, con toque ultraseco y efecto matificante; para uso en el rostro y piel mixta a grasa. Dermatológicamente probado, no comedogénico. Disponible en 3 tonos: sin color, claro y oscuro.
+Ingredientes activos: Combinación de algas rojas y marrones (hidratan y mejoran la tolerabilidad de los demás componentes) y Ácido hialurónico de origen vegano (0,5%) con moléculas de bajo, medio y alto peso molecular. Ingredientes de origen natural.</t>
+  </si>
+  <si>
+    <t>30 ml</t>
+  </si>
+  <si>
+    <t>Beneficios: Contiene 21 ingredientes de origen natural con potente acción restauradora y protectora de la barrera cutánea. Ayuda a restaurar, proteger y restablecer la función de barrera de la piel. Protege las células de la deshidratación reduciendo la pérdida transepidérmica de agua (TEWL) y previene que los alérgenos penetren en la piel. Apta para bebés, niños y adultos.
+Ingredientes activos: Ectoína (post-biótico humectante), Crema lamelar (con Escualeno y Ceramida 3) y Extracto de corteza de avellana.</t>
+  </si>
+  <si>
+    <t>Beneficios: Crema corporal hidratante y emoliente que contiene 29 ingredientes de origen natural, ofreciendo hidratación y cuidado diario de pieles secas y sensibles. Protege la barrera cutánea. Humecta, mejora la suavidad y aumenta la elasticidad de la piel en más de 90%. Apta para bebés, niños y adultos. Dermatológicamente probado, no comedogénico.
+Ingredientes activos: Aceite de grosella negra (antioxidante), Manteca de karité (hidratante), Aceite de coco (antioxidante), Extracto de vainilla (antioxidante y calmante), Extracto de hoja de romero (protector antienvejecimiento, antioxidante) y Aceite de girasol (antioxidante).</t>
+  </si>
+  <si>
+    <t>Cuidado Labial</t>
+  </si>
+  <si>
+    <t>Atopeel Bálsamo Lip Protect</t>
+  </si>
+  <si>
+    <t>Sabores: vainilla y menta</t>
+  </si>
+  <si>
+    <t>Beneficios: Bálsamo labial que humecta, repara y protege los labios frente a diferentes condiciones climáticas. Genera cuatro beneficios para labios sensibles y resecos: emoliente e hidratante, reparador y protector, antioxidante y calmante. Con activos vegetales emolientes, reparadores y protectores que reducen la irritación e inflamación de la piel. 93% ingredientes de origen natural. Disponible en 2 sabores: vainilla y menta.
+Ingredientes activos: Aceite de jojoba (10%), Fitocomplejo (5%) con ésteres de jojoba, girasol, karité y mimosa; Caléndula y Vitamina E natural (0,5%).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -688,8 +2085,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -702,8 +2115,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E7D32"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -711,20 +2130,67 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBDBDBD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBDBDBD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBDBDBD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBDBDBD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1037,9 +2503,31 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="4">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{1954D7C5-27C1-4A86-AD2E-CE6AE5377477}">
+  <we:reference id="WA200009404" version="1.0.0.8" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;3c89ebb2-96a6-40c8-8c2e-b0f11a9014b4&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{013C7B1A-6F96-4AFC-A80B-4018FB53EECE}">
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.28515625" bestFit="1" customWidth="1"/>
@@ -1074,7 +2562,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
@@ -1091,7 +2579,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
@@ -1108,7 +2596,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="B4" t="s">
@@ -1125,7 +2613,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" t="s">
         <v>0</v>
       </c>
       <c r="B5" t="s">
@@ -1142,7 +2630,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" t="s">
         <v>0</v>
       </c>
       <c r="B6" t="s">
@@ -1159,7 +2647,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" t="s">
         <v>0</v>
       </c>
       <c r="B7" t="s">
@@ -1176,7 +2664,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" t="s">
         <v>0</v>
       </c>
       <c r="B8" t="s">
@@ -1193,7 +2681,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" t="s">
         <v>0</v>
       </c>
       <c r="B9" t="s">
@@ -1210,7 +2698,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" t="s">
         <v>0</v>
       </c>
       <c r="B10" t="s">
@@ -1227,7 +2715,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" t="s">
         <v>0</v>
       </c>
       <c r="B11" t="s">
@@ -1244,7 +2732,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" t="s">
         <v>0</v>
       </c>
       <c r="B12" t="s">
@@ -1261,7 +2749,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" t="s">
         <v>0</v>
       </c>
       <c r="B13" t="s">
@@ -1278,7 +2766,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="A14" t="s">
         <v>0</v>
       </c>
       <c r="B14" t="s">
@@ -1295,7 +2783,7 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+      <c r="A15" t="s">
         <v>0</v>
       </c>
       <c r="B15" t="s">
@@ -1312,7 +2800,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="A16" t="s">
         <v>0</v>
       </c>
       <c r="B16" t="s">
@@ -1327,18 +2815,18 @@
       <c r="E16" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+      <c r="A17" t="s">
         <v>0</v>
       </c>
       <c r="B17" t="s">
         <v>56</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" t="s">
         <v>57</v>
       </c>
       <c r="D17" t="s">
@@ -1349,7 +2837,7 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="A18" t="s">
         <v>60</v>
       </c>
       <c r="B18" t="s">
@@ -1364,765 +2852,3449 @@
       <c r="E18" t="s">
         <v>62</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+      <c r="A19" t="s">
         <v>63</v>
       </c>
       <c r="B19" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" t="s">
         <v>64</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" t="s">
         <v>65</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" t="s">
         <v>66</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="A20" t="s">
         <v>0</v>
       </c>
       <c r="B20" t="s">
         <v>68</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" t="s">
         <v>69</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" t="s">
         <v>70</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
+      <c r="A21" t="s">
         <v>0</v>
       </c>
       <c r="B21" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" t="s">
         <v>72</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" t="s">
         <v>74</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
+      <c r="A22" t="s">
         <v>0</v>
       </c>
       <c r="B22" t="s">
         <v>68</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" t="s">
         <v>75</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" t="s">
         <v>76</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+      <c r="A23" t="s">
         <v>0</v>
       </c>
       <c r="B23" t="s">
         <v>78</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" t="s">
         <v>79</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" t="s">
         <v>81</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="A24" t="s">
         <v>0</v>
       </c>
       <c r="B24" t="s">
         <v>78</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" t="s">
         <v>82</v>
       </c>
       <c r="D24" t="s">
         <v>83</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
+      <c r="A25" t="s">
         <v>0</v>
       </c>
       <c r="B25" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" t="s">
         <v>85</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" t="s">
         <v>86</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
+      <c r="A26" t="s">
         <v>63</v>
       </c>
       <c r="B26" t="s">
         <v>88</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" t="s">
         <v>89</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" t="s">
         <v>90</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" t="s">
         <v>91</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
+      <c r="A27" t="s">
         <v>0</v>
       </c>
       <c r="B27" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" t="s">
         <v>92</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" t="s">
         <v>93</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
+      <c r="A28" t="s">
         <v>0</v>
       </c>
       <c r="B28" t="s">
         <v>88</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" t="s">
         <v>95</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" t="s">
         <v>96</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
+      <c r="A29" t="s">
         <v>0</v>
       </c>
       <c r="B29" t="s">
         <v>88</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" t="s">
         <v>98</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" t="s">
         <v>100</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
+      <c r="A30" t="s">
         <v>60</v>
       </c>
       <c r="B30" t="s">
         <v>88</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" t="s">
         <v>101</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" t="s">
         <v>102</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" t="s">
         <v>103</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
+      <c r="A31" t="s">
         <v>0</v>
       </c>
       <c r="B31" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" t="s">
         <v>105</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" t="s">
         <v>106</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
+      <c r="A32" t="s">
         <v>0</v>
       </c>
       <c r="B32" t="s">
         <v>104</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" t="s">
         <v>108</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" t="s">
         <v>110</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
+      <c r="A33" t="s">
         <v>0</v>
       </c>
       <c r="B33" t="s">
         <v>104</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" t="s">
         <v>111</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" t="s">
         <v>112</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
+      <c r="A34" t="s">
         <v>60</v>
       </c>
       <c r="B34" t="s">
         <v>114</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" t="s">
         <v>115</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" t="s">
         <v>116</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
+      <c r="A35" t="s">
         <v>0</v>
       </c>
       <c r="B35" t="s">
         <v>118</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" t="s">
         <v>121</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" t="s">
         <v>120</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
+      <c r="A36" t="s">
         <v>0</v>
       </c>
       <c r="B36" t="s">
         <v>122</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" t="s">
         <v>123</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" t="s">
         <v>124</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
+      <c r="A37" t="s">
         <v>0</v>
       </c>
       <c r="B37" t="s">
         <v>122</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" t="s">
         <v>126</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" t="s">
         <v>127</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
+      <c r="A38" t="s">
         <v>0</v>
       </c>
       <c r="B38" t="s">
         <v>122</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" t="s">
         <v>129</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" t="s">
         <v>130</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E38" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
+      <c r="A39" t="s">
         <v>0</v>
       </c>
       <c r="B39" t="s">
         <v>132</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" t="s">
         <v>133</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" t="s">
         <v>134</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="A40" t="s">
         <v>0</v>
       </c>
       <c r="B40" t="s">
         <v>132</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" t="s">
         <v>138</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" t="s">
         <v>136</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" s="2" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
+      <c r="A42" t="s">
         <v>0</v>
       </c>
       <c r="B42" t="s">
         <v>139</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" t="s">
         <v>140</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" t="s">
         <v>141</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E42" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
+      <c r="A43" t="s">
         <v>0</v>
       </c>
       <c r="B43" t="s">
         <v>143</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" t="s">
         <v>144</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" t="s">
         <v>145</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E43" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
+      <c r="A44" t="s">
         <v>0</v>
       </c>
       <c r="B44" t="s">
         <v>147</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" t="s">
         <v>148</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D44" t="s">
         <v>149</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E44" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
+      <c r="A45" t="s">
         <v>0</v>
       </c>
       <c r="B45" t="s">
         <v>147</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" t="s">
         <v>151</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D45" t="s">
         <v>152</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
+      <c r="A46" t="s">
         <v>0</v>
       </c>
       <c r="B46" t="s">
         <v>147</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" t="s">
         <v>154</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" t="s">
         <v>155</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="E46" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
+      <c r="A47" t="s">
         <v>0</v>
       </c>
       <c r="B47" t="s">
         <v>147</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" t="s">
         <v>157</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" t="s">
         <v>158</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E47" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
+      <c r="A48" t="s">
         <v>0</v>
       </c>
       <c r="B48" t="s">
         <v>160</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" t="s">
         <v>161</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D48" t="s">
         <v>163</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="E48" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
+      <c r="A49" t="s">
         <v>0</v>
       </c>
       <c r="B49" t="s">
         <v>160</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" t="s">
         <v>164</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D49" t="s">
         <v>166</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="E49" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
+      <c r="A50" t="s">
         <v>0</v>
       </c>
       <c r="B50" t="s">
         <v>160</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" t="s">
         <v>167</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" t="s">
         <v>168</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E50" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
+      <c r="A51" t="s">
         <v>0</v>
       </c>
       <c r="B51" t="s">
         <v>160</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" t="s">
         <v>170</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" t="s">
         <v>171</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="E51" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="5" t="s">
+      <c r="A52" t="s">
         <v>0</v>
       </c>
       <c r="B52" t="s">
         <v>160</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" t="s">
         <v>173</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D52" t="s">
         <v>174</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="E52" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
+      <c r="A53" t="s">
         <v>0</v>
       </c>
       <c r="B53" t="s">
         <v>160</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" t="s">
         <v>176</v>
       </c>
       <c r="D53" t="s">
         <v>177</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="E53" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
+      <c r="A54" t="s">
         <v>0</v>
       </c>
       <c r="B54" t="s">
         <v>179</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" t="s">
         <v>180</v>
       </c>
       <c r="D54" t="s">
         <v>181</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="E54" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="5" t="s">
+      <c r="A55" t="s">
         <v>0</v>
       </c>
       <c r="B55" t="s">
         <v>179</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" t="s">
         <v>183</v>
       </c>
       <c r="D55" t="s">
         <v>184</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="E55" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="s">
+      <c r="A56" t="s">
         <v>0</v>
       </c>
       <c r="B56" t="s">
         <v>179</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" t="s">
         <v>186</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D56" t="s">
         <v>187</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="E56" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
+      <c r="A57" t="s">
         <v>0</v>
       </c>
       <c r="B57" t="s">
         <v>179</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" t="s">
         <v>189</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="D57" t="s">
         <v>190</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="E57" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="5" t="s">
+      <c r="A58" t="s">
         <v>0</v>
       </c>
       <c r="B58" t="s">
         <v>179</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" t="s">
         <v>192</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D58" t="s">
         <v>194</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="E58" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
+      <c r="A59" t="s">
         <v>0</v>
       </c>
       <c r="B59" t="s">
         <v>179</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" t="s">
         <v>195</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="D59" t="s">
         <v>196</v>
       </c>
-      <c r="E59" s="2" t="s">
+      <c r="E59" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="5" t="s">
+      <c r="A60" t="s">
         <v>0</v>
       </c>
       <c r="B60" t="s">
         <v>198</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" t="s">
         <v>200</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D60" t="s">
         <v>199</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="E60" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="5" t="s">
+      <c r="A61" t="s">
         <v>0</v>
       </c>
       <c r="B61" t="s">
         <v>198</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" t="s">
         <v>202</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="D61" t="s">
         <v>203</v>
       </c>
-      <c r="E61" s="2" t="s">
+      <c r="E61" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="5" t="s">
+      <c r="A62" t="s">
         <v>0</v>
       </c>
       <c r="B62" t="s">
         <v>198</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" t="s">
         <v>205</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D62" t="s">
         <v>207</v>
       </c>
-      <c r="E62" s="2" t="s">
+      <c r="E62" t="s">
         <v>206</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C63" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C64" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="65" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C65" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="66" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C66" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="67" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C67" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="68" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C68" t="s">
+        <v>219</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C585DF6-9D8F-432B-9BFE-033CDE4DC717}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.7109375" customWidth="1"/>
+    <col min="2" max="2" width="28.5703125" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" customWidth="1"/>
+    <col min="6" max="6" width="72.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="95.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="D2" s="5">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="95.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="D3" s="5">
+        <v>2</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="95.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D4" s="5">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="95.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="D5" s="5">
+        <v>4</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="95.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="D6" s="5">
+        <v>5</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="D7" s="5">
+        <v>6</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D8" s="5">
+        <v>7</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="D9" s="5">
+        <v>8</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="D10" s="5">
+        <v>9</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D11" s="5">
+        <v>10</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="D12" s="5">
+        <v>11</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F168784-69CC-41CF-AF5C-5BEBF259363F}">
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="106.7109375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="11.42578125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D2" s="5">
+        <v>1</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="D3" s="5">
+        <v>2</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="D4" s="5">
+        <v>3</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="D5" s="5">
+        <v>4</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="D6" s="5">
+        <v>5</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="D7" s="5">
+        <v>6</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="D8" s="5">
+        <v>7</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="D9" s="5">
+        <v>8</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="D10" s="5">
+        <v>9</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="D11" s="5">
+        <v>10</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="D12" s="5">
+        <v>11</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="D13" s="5">
+        <v>12</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="D14" s="5">
+        <v>13</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="D15" s="5">
+        <v>14</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="D16" s="5">
+        <v>15</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="D17" s="5">
+        <v>16</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="D18" s="5">
+        <v>17</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="D19" s="5">
+        <v>18</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="D20" s="5">
+        <v>19</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="D21" s="5">
+        <v>20</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="D22" s="5">
+        <v>21</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="D23" s="5">
+        <v>22</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="D24" s="5">
+        <v>23</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="D25" s="5">
+        <v>24</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="D26" s="5">
+        <v>25</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="D27" s="5">
+        <v>26</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="D28" s="5">
+        <v>27</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="D29" s="5">
+        <v>28</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="D30" s="5">
+        <v>29</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="D31" s="5">
+        <v>30</v>
+      </c>
+      <c r="E31" s="5"/>
+      <c r="F31" s="4" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="D32" s="5">
+        <v>31</v>
+      </c>
+      <c r="E32" s="5"/>
+      <c r="F32" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="D33" s="5">
+        <v>32</v>
+      </c>
+      <c r="E33" s="5"/>
+      <c r="F33" s="4" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="D34" s="5">
+        <v>33</v>
+      </c>
+      <c r="E34" s="5"/>
+      <c r="F34" s="4" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="D35" s="5">
+        <v>34</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>455</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E2F8625-D89E-483A-9F31-74D0EE8A5717}">
+  <dimension ref="A1:F82"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="31.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="106.7109375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="11.42578125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D2" s="5">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D3" s="5">
+        <v>2</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="D4" s="5">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="D5" s="5">
+        <v>4</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="D6" s="5">
+        <v>5</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="D7" s="5">
+        <v>6</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="D8" s="5">
+        <v>7</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="D9" s="5">
+        <v>8</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="D10" s="5">
+        <v>9</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="D11" s="5">
+        <v>10</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="D12" s="5">
+        <v>11</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="D13" s="5">
+        <v>12</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="D14" s="5">
+        <v>13</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="D15" s="5">
+        <v>14</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="D16" s="5">
+        <v>15</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="D17" s="5">
+        <v>16</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D18" s="5">
+        <v>17</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="D19" s="5">
+        <v>18</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="D20" s="5">
+        <v>19</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="D21" s="5">
+        <v>20</v>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="D22" s="5">
+        <v>21</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="D23" s="5">
+        <v>22</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="D24" s="5">
+        <v>23</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="D25" s="5">
+        <v>24</v>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="D26" s="5">
+        <v>25</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="D27" s="5">
+        <v>26</v>
+      </c>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="D28" s="5">
+        <v>27</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="D29" s="5">
+        <v>28</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D30" s="5">
+        <v>29</v>
+      </c>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="D31" s="5">
+        <v>30</v>
+      </c>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="D32" s="5">
+        <v>31</v>
+      </c>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="D33" s="5">
+        <v>32</v>
+      </c>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="D34" s="5">
+        <v>33</v>
+      </c>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="D35" s="5">
+        <v>34</v>
+      </c>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="D36" s="5">
+        <v>35</v>
+      </c>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="D37" s="5">
+        <v>36</v>
+      </c>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="D38" s="5">
+        <v>37</v>
+      </c>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="D39" s="5">
+        <v>38</v>
+      </c>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="D40" s="5">
+        <v>39</v>
+      </c>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="D41" s="5">
+        <v>40</v>
+      </c>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="D42" s="5">
+        <v>41</v>
+      </c>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="D43" s="5">
+        <v>42</v>
+      </c>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="D44" s="5">
+        <v>43</v>
+      </c>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="D45" s="5">
+        <v>44</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="D46" s="5">
+        <v>45</v>
+      </c>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D47" s="5">
+        <v>46</v>
+      </c>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="D48" s="5">
+        <v>47</v>
+      </c>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="D49" s="5">
+        <v>48</v>
+      </c>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="D50" s="5">
+        <v>49</v>
+      </c>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="D51" s="5">
+        <v>50</v>
+      </c>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="D52" s="5">
+        <v>51</v>
+      </c>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="D53" s="5">
+        <v>52</v>
+      </c>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="D54" s="5">
+        <v>53</v>
+      </c>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="D55" s="5">
+        <v>54</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="D56" s="5">
+        <v>55</v>
+      </c>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="D57" s="5">
+        <v>56</v>
+      </c>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="D58" s="5">
+        <v>57</v>
+      </c>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="D59" s="5">
+        <v>58</v>
+      </c>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="D60" s="5">
+        <v>59</v>
+      </c>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="D61" s="5">
+        <v>60</v>
+      </c>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="D62" s="5">
+        <v>61</v>
+      </c>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="D63" s="5">
+        <v>62</v>
+      </c>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="D64" s="5">
+        <v>63</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="D65" s="5">
+        <v>64</v>
+      </c>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="D66" s="5">
+        <v>65</v>
+      </c>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="D67" s="5">
+        <v>66</v>
+      </c>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="D68" s="5">
+        <v>67</v>
+      </c>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="D69" s="5">
+        <v>68</v>
+      </c>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="D70" s="5">
+        <v>69</v>
+      </c>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="D71" s="5">
+        <v>70</v>
+      </c>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="D72" s="5">
+        <v>71</v>
+      </c>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="D73" s="5">
+        <v>72</v>
+      </c>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="D74" s="5">
+        <v>73</v>
+      </c>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="D75" s="5">
+        <v>74</v>
+      </c>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="D76" s="5">
+        <v>75</v>
+      </c>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="D77" s="5">
+        <v>76</v>
+      </c>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="D78" s="5">
+        <v>77</v>
+      </c>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="D79" s="5">
+        <v>78</v>
+      </c>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="D80" s="5">
+        <v>79</v>
+      </c>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="D81" s="5">
+        <v>80</v>
+      </c>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="D82" s="5">
+        <v>81</v>
+      </c>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4" t="s">
+        <v>419</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{061F5A37-75D1-4EB5-844D-F1E48A58B71B}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" customWidth="1"/>
+    <col min="6" max="6" width="114.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="170.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>527</v>
+      </c>
+      <c r="D2" s="9">
+        <v>1</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="170.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>529</v>
+      </c>
+      <c r="D3" s="9">
+        <v>2</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="170.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>532</v>
+      </c>
+      <c r="D4" s="9">
+        <v>3</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="170.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>534</v>
+      </c>
+      <c r="D5" s="9">
+        <v>4</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="170.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>542</v>
+      </c>
+      <c r="D6" s="9">
+        <v>5</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>543</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="170.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="D7" s="9">
+        <v>6</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="170.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>525</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>550</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>551</v>
+      </c>
+      <c r="D8" s="14">
+        <v>7</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>552</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>553</v>
       </c>
     </row>
   </sheetData>
